--- a/Result/RBM_LowDepthQAE_eps=0.0025_nShot=12.xlsx
+++ b/Result/RBM_LowDepthQAE_eps=0.0025_nShot=12.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\koich\Desktop\Code\DivQCOSDE\Result\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6290F25A-007D-491E-81B6-FC1B19F7A4E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D938CE0-B440-4D5B-B322-7CC9736D2868}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-255" yWindow="1290" windowWidth="18390" windowHeight="9015" xr2:uid="{8730DC5B-5742-49A9-9164-FF6EA95AD078}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="18390" windowHeight="9015" xr2:uid="{8730DC5B-5742-49A9-9164-FF6EA95AD078}"/>
   </bookViews>
   <sheets>
     <sheet name="RBM_LowDepthQAE" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
   <si>
     <t>N</t>
   </si>
@@ -54,10 +54,6 @@
   </si>
   <si>
     <t>maxDepth</t>
-  </si>
-  <si>
-    <t>absErrAve</t>
-    <phoneticPr fontId="18"/>
   </si>
   <si>
     <t>errSq</t>
@@ -802,7 +798,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>RBM_LowDepthQAE!$M$1</c:f>
+              <c:f>RBM_LowDepthQAE!$L$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -873,33 +869,33 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>RBM_LowDepthQAE!$M$2:$M$10</c:f>
+              <c:f>RBM_LowDepthQAE!$L$2:$L$10</c:f>
               <c:numCache>
                 <c:formatCode>#,##0_);[Red]\(#,##0\)</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>516240</c:v>
+                  <c:v>354240</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1021680</c:v>
+                  <c:v>794376</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>2134656</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5486052</c:v>
+                  <c:v>4936536</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>13330944</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>34428240</c:v>
+                  <c:v>32900580</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>83566080</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>210073500</c:v>
+                  <c:v>205896600</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>520722432</c:v>
@@ -1159,7 +1155,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>RBM_LowDepthQAE!$N$1</c:f>
+              <c:f>RBM_LowDepthQAE!$M$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1230,27 +1226,27 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>RBM_LowDepthQAE!$N$2:$N$10</c:f>
+              <c:f>RBM_LowDepthQAE!$M$2:$M$10</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>3000</c:v>
+                  <c:v>2264</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3157</c:v>
+                  <c:v>2651</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>3216</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3982</c:v>
+                  <c:v>3762</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>4512</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5535</c:v>
+                  <c:v>5355</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>6464</c:v>
@@ -2969,20 +2965,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{453854F1-4FBD-4AEA-85B6-FB1EDDD605AA}">
-  <dimension ref="A1:Q899"/>
+  <dimension ref="A1:P899"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="7" max="7" width="10.5" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13.375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.625" customWidth="1"/>
+    <col min="13" max="14" width="10.25" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="9.5" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="15.5" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="10.5" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="9.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2999,7 +2995,7 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G1" t="s">
         <v>5</v>
@@ -3011,19 +3007,16 @@
         <v>0</v>
       </c>
       <c r="K1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L1" t="s">
         <v>9</v>
       </c>
       <c r="M1" t="s">
-        <v>10</v>
-      </c>
-      <c r="N1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>8</v>
       </c>
@@ -3034,43 +3027,40 @@
         <v>0.173533659869819</v>
       </c>
       <c r="D2">
-        <v>0.64958649586495798</v>
-      </c>
-      <c r="E2" s="1">
-        <v>1.8271554969140299E-5</v>
+        <v>0.64936493649364901</v>
+      </c>
+      <c r="E2">
+        <v>2.39830926278439E-4</v>
       </c>
       <c r="F2">
         <f>E2*E2</f>
-        <v>3.3384972099031555E-10</v>
+        <v>5.7518873199574041E-8</v>
       </c>
       <c r="G2">
-        <v>516240</v>
+        <v>354240</v>
       </c>
       <c r="H2">
-        <v>3000</v>
+        <v>2264</v>
       </c>
       <c r="J2">
         <v>8</v>
       </c>
       <c r="K2" s="3">
-        <v>2.78370539849384E-3</v>
-      </c>
-      <c r="L2" s="3">
         <f>SQRT(AVERAGEIF($A$2:$A$1048576,$J2,$F$2:$F$1048576))</f>
-        <v>5.0408152262239379E-4</v>
-      </c>
-      <c r="M2" s="2">
-        <f t="shared" ref="M2:M10" si="0">AVERAGEIF($A$2:$A$1048576,$J2,$G$2:$G$1048576)</f>
-        <v>516240</v>
-      </c>
-      <c r="N2" s="4">
-        <f t="shared" ref="N2:N10" si="1">AVERAGEIF($A$2:$A$1048576,$J2,$H$2:$H$1048576)</f>
-        <v>3000</v>
-      </c>
+        <v>3.5129106370323967E-4</v>
+      </c>
+      <c r="L2" s="2">
+        <f t="shared" ref="L2:L10" si="0">AVERAGEIF($A$2:$A$1048576,$J2,$G$2:$G$1048576)</f>
+        <v>354240</v>
+      </c>
+      <c r="M2" s="4">
+        <f t="shared" ref="M2:M10" si="1">AVERAGEIF($A$2:$A$1048576,$J2,$H$2:$H$1048576)</f>
+        <v>2264</v>
+      </c>
+      <c r="O2" s="2"/>
       <c r="P2" s="2"/>
-      <c r="Q2" s="2"/>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>11</v>
       </c>
@@ -3081,43 +3071,40 @@
         <v>0.20010927661716699</v>
       </c>
       <c r="D3">
-        <v>0.65002650026500197</v>
+        <v>0.64986498649864899</v>
       </c>
       <c r="E3">
-        <v>4.2173284507485099E-4</v>
+        <v>2.6021907872209E-4</v>
       </c>
       <c r="F3">
         <f t="shared" ref="F3:F66" si="2">E3*E3</f>
-        <v>1.7785859261492827E-7</v>
+        <v>6.7713968930973274E-8</v>
       </c>
       <c r="G3">
-        <v>1021680</v>
+        <v>794376</v>
       </c>
       <c r="H3">
-        <v>3157</v>
+        <v>2651</v>
       </c>
       <c r="J3">
         <v>11</v>
       </c>
       <c r="K3" s="3">
-        <v>2.6084647076070398E-3</v>
-      </c>
-      <c r="L3" s="3">
-        <f t="shared" ref="L3:L8" si="3">SQRT(AVERAGEIF($A$2:$A$1048576,$J3,$F$2:$F$1048576))</f>
-        <v>4.7845777349575898E-4</v>
-      </c>
-      <c r="M3" s="2">
+        <f t="shared" ref="K3:K8" si="3">SQRT(AVERAGEIF($A$2:$A$1048576,$J3,$F$2:$F$1048576))</f>
+        <v>3.7803910320595473E-4</v>
+      </c>
+      <c r="L3" s="2">
         <f t="shared" si="0"/>
-        <v>1021680</v>
-      </c>
-      <c r="N3" s="4">
+        <v>794376</v>
+      </c>
+      <c r="M3" s="4">
         <f t="shared" si="1"/>
-        <v>3157</v>
-      </c>
+        <v>2651</v>
+      </c>
+      <c r="O3" s="2"/>
       <c r="P3" s="2"/>
-      <c r="Q3" s="2"/>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>16</v>
       </c>
@@ -3128,14 +3115,14 @@
         <v>0.23137821315975901</v>
       </c>
       <c r="D4">
-        <v>0.64932649326493197</v>
+        <v>0.64986498649864899</v>
       </c>
       <c r="E4">
-        <v>2.7827415499514997E-4</v>
+        <v>2.6021907872209E-4</v>
       </c>
       <c r="F4">
         <f t="shared" si="2"/>
-        <v>7.743650533826475E-8</v>
+        <v>6.7713968930973274E-8</v>
       </c>
       <c r="G4">
         <v>2134656</v>
@@ -3147,24 +3134,21 @@
         <v>16</v>
       </c>
       <c r="K4" s="3">
-        <v>2.90206703988628E-3</v>
-      </c>
-      <c r="L4" s="3">
         <f t="shared" si="3"/>
-        <v>3.5774101414679844E-4</v>
-      </c>
-      <c r="M4" s="2">
+        <v>2.1637264730050857E-4</v>
+      </c>
+      <c r="L4" s="2">
         <f t="shared" si="0"/>
         <v>2134656</v>
       </c>
-      <c r="N4" s="4">
+      <c r="M4" s="4">
         <f t="shared" si="1"/>
         <v>3216</v>
       </c>
-      <c r="P4" s="5"/>
-      <c r="Q4" s="2"/>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="O4" s="5"/>
+      <c r="P4" s="2"/>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>22</v>
       </c>
@@ -3175,43 +3159,40 @@
         <v>0.25795382990710702</v>
       </c>
       <c r="D5">
-        <v>0.64959649596495905</v>
-      </c>
-      <c r="E5" s="1">
-        <v>8.2714549681783805E-6</v>
+        <v>0.65016501650165004</v>
+      </c>
+      <c r="E5">
+        <v>5.60249081722363E-4</v>
       </c>
       <c r="F5">
         <f t="shared" si="2"/>
-        <v>6.8416967290602813E-11</v>
+        <v>3.1387903357075096E-7</v>
       </c>
       <c r="G5">
-        <v>5486052</v>
+        <v>4936536</v>
       </c>
       <c r="H5">
-        <v>3982</v>
+        <v>3762</v>
       </c>
       <c r="J5">
         <v>22</v>
       </c>
       <c r="K5" s="3">
-        <v>2.6614507005249199E-3</v>
-      </c>
-      <c r="L5" s="3">
         <f t="shared" si="3"/>
-        <v>3.6483463443787357E-4</v>
-      </c>
-      <c r="M5" s="2">
+        <v>3.0991956283493092E-4</v>
+      </c>
+      <c r="L5" s="2">
         <f t="shared" si="0"/>
-        <v>5486052</v>
-      </c>
-      <c r="N5" s="4">
+        <v>4936536</v>
+      </c>
+      <c r="M5" s="4">
         <f t="shared" si="1"/>
-        <v>3982</v>
-      </c>
+        <v>3762</v>
+      </c>
+      <c r="O5" s="2"/>
       <c r="P5" s="2"/>
-      <c r="Q5" s="2"/>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>32</v>
       </c>
@@ -3222,14 +3203,14 @@
         <v>0.28922276644969802</v>
       </c>
       <c r="D6">
-        <v>0.64992649926499202</v>
-      </c>
-      <c r="E6">
-        <v>3.2173184506489801E-4</v>
+        <v>0.64956495649564905</v>
+      </c>
+      <c r="E6" s="1">
+        <v>3.9810924278183002E-5</v>
       </c>
       <c r="F6">
         <f t="shared" si="2"/>
-        <v>1.0351138012886354E-7</v>
+        <v>1.5849096918832207E-9</v>
       </c>
       <c r="G6">
         <v>13330944</v>
@@ -3241,24 +3222,21 @@
         <v>32</v>
       </c>
       <c r="K6" s="3">
-        <v>2.2686345857311401E-3</v>
-      </c>
-      <c r="L6" s="3">
         <f t="shared" si="3"/>
-        <v>3.8037744041779955E-4</v>
-      </c>
-      <c r="M6" s="2">
+        <v>2.2002208691534236E-4</v>
+      </c>
+      <c r="L6" s="2">
         <f t="shared" si="0"/>
         <v>13330944</v>
       </c>
-      <c r="N6" s="4">
+      <c r="M6" s="4">
         <f t="shared" si="1"/>
         <v>4512</v>
       </c>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="2"/>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="O6" s="5"/>
+      <c r="P6" s="2"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>45</v>
       </c>
@@ -3269,43 +3247,40 @@
         <v>0.31767378909116201</v>
       </c>
       <c r="D7">
-        <v>0.64932649326493197</v>
+        <v>0.65026502650264995</v>
       </c>
       <c r="E7">
-        <v>2.7827415499514997E-4</v>
+        <v>6.6025908272249103E-4</v>
       </c>
       <c r="F7">
         <f t="shared" si="2"/>
-        <v>7.743650533826475E-8</v>
+        <v>4.3594205631754526E-7</v>
       </c>
       <c r="G7">
-        <v>34428240</v>
+        <v>32900580</v>
       </c>
       <c r="H7">
-        <v>5535</v>
+        <v>5355</v>
       </c>
       <c r="J7">
         <v>45</v>
       </c>
       <c r="K7" s="3">
-        <v>2.2982298229822901E-3</v>
-      </c>
-      <c r="L7" s="3">
         <f t="shared" si="3"/>
-        <v>2.5644174952621431E-4</v>
-      </c>
-      <c r="M7" s="2">
+        <v>2.6803252189438526E-4</v>
+      </c>
+      <c r="L7" s="2">
         <f t="shared" si="0"/>
-        <v>34428240</v>
-      </c>
-      <c r="N7" s="4">
+        <v>32900580</v>
+      </c>
+      <c r="M7" s="4">
         <f t="shared" si="1"/>
-        <v>5535</v>
-      </c>
+        <v>5355</v>
+      </c>
+      <c r="O7" s="2"/>
       <c r="P7" s="2"/>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>64</v>
       </c>
@@ -3316,14 +3291,14 @@
         <v>0.347067319739638</v>
       </c>
       <c r="D8">
-        <v>0.64982649826498196</v>
+        <v>0.64946494649464903</v>
       </c>
       <c r="E8">
-        <v>2.21730845054834E-4</v>
+        <v>1.39820925278311E-4</v>
       </c>
       <c r="F8">
         <f t="shared" si="2"/>
-        <v>4.9164567648730803E-8</v>
+        <v>1.9549891145683028E-8</v>
       </c>
       <c r="G8">
         <v>83566080</v>
@@ -3335,24 +3310,21 @@
         <v>64</v>
       </c>
       <c r="K8" s="3">
-        <v>2.1268242658354398E-3</v>
-      </c>
-      <c r="L8" s="3">
         <f t="shared" si="3"/>
-        <v>3.5348691092196624E-4</v>
-      </c>
-      <c r="M8" s="2">
+        <v>2.7255871985428431E-4</v>
+      </c>
+      <c r="L8" s="2">
         <f t="shared" si="0"/>
         <v>83566080</v>
       </c>
-      <c r="N8" s="4">
+      <c r="M8" s="4">
         <f t="shared" si="1"/>
         <v>6464</v>
       </c>
+      <c r="O8" s="5"/>
       <c r="P8" s="5"/>
-      <c r="Q8" s="5"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>90</v>
       </c>
@@ -3363,17 +3335,17 @@
         <v>0.37551834238110199</v>
       </c>
       <c r="D9">
-        <v>0.64955649556495498</v>
-      </c>
-      <c r="E9" s="1">
-        <v>4.8271854972137202E-5</v>
+        <v>0.649264926492649</v>
+      </c>
+      <c r="E9">
+        <v>3.39840927278456E-4</v>
       </c>
       <c r="F9">
         <f t="shared" si="2"/>
-        <v>2.3301719824510472E-9</v>
+        <v>1.1549185585348082E-7</v>
       </c>
       <c r="G9">
-        <v>210073500</v>
+        <v>205896600</v>
       </c>
       <c r="H9">
         <v>7650</v>
@@ -3382,24 +3354,21 @@
         <v>90</v>
       </c>
       <c r="K9" s="3">
-        <v>2.04179645737317E-3</v>
-      </c>
-      <c r="L9" s="3">
         <f>SQRT(AVERAGEIF($A$2:$A$1048576,$J9,$F$2:$F$1048576))</f>
-        <v>2.560525063368965E-4</v>
-      </c>
-      <c r="M9" s="2">
+        <v>2.6226495014324122E-4</v>
+      </c>
+      <c r="L9" s="2">
         <f t="shared" si="0"/>
-        <v>210073500</v>
-      </c>
-      <c r="N9" s="4">
+        <v>205896600</v>
+      </c>
+      <c r="M9" s="4">
         <f t="shared" si="1"/>
         <v>7650</v>
       </c>
+      <c r="O9" s="2"/>
       <c r="P9" s="2"/>
-      <c r="Q9" s="2"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.4">
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>128</v>
       </c>
@@ -3410,14 +3379,14 @@
         <v>0.40491187302957798</v>
       </c>
       <c r="D10">
-        <v>0.64945649456494503</v>
-      </c>
-      <c r="E10">
-        <v>1.48272854982201E-4</v>
+        <v>0.64956495649564905</v>
+      </c>
+      <c r="E10" s="1">
+        <v>3.9810924278183002E-5</v>
       </c>
       <c r="F10">
         <f t="shared" si="2"/>
-        <v>2.1984839524572808E-8</v>
+        <v>1.5849096918832207E-9</v>
       </c>
       <c r="G10">
         <v>520722432</v>
@@ -3429,24 +3398,21 @@
         <v>128</v>
       </c>
       <c r="K10" s="3">
-        <v>3.9390247915694204E-3</v>
-      </c>
-      <c r="L10" s="3">
         <f>SQRT(AVERAGEIF($A$2:$A$1048576,$J10,$F$2:$F$1048576))</f>
-        <v>3.4724584113568778E-4</v>
-      </c>
-      <c r="M10" s="2">
+        <v>2.1551783628471748E-4</v>
+      </c>
+      <c r="L10" s="2">
         <f t="shared" si="0"/>
         <v>520722432</v>
       </c>
-      <c r="N10" s="4">
+      <c r="M10" s="4">
         <f t="shared" si="1"/>
         <v>9088</v>
       </c>
-      <c r="P10" s="5"/>
-      <c r="Q10" s="2"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="O10" s="5"/>
+      <c r="P10" s="2"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>8</v>
       </c>
@@ -3457,23 +3423,23 @@
         <v>0.173533659869819</v>
       </c>
       <c r="D11">
-        <v>0.64950649506494995</v>
-      </c>
-      <c r="E11" s="1">
-        <v>9.8272354977169102E-5</v>
+        <v>0.64896489648964895</v>
+      </c>
+      <c r="E11">
+        <v>6.3987093027884003E-4</v>
       </c>
       <c r="F11">
         <f t="shared" si="2"/>
-        <v>9.6574557527587323E-9</v>
+        <v>4.0943480741590816E-7</v>
       </c>
       <c r="G11">
-        <v>516240</v>
+        <v>354240</v>
       </c>
       <c r="H11">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.4">
+        <v>2264</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>11</v>
       </c>
@@ -3484,23 +3450,23 @@
         <v>0.20010927661716699</v>
       </c>
       <c r="D12">
-        <v>0.64951649516495102</v>
-      </c>
-      <c r="E12" s="1">
-        <v>8.8272254976096102E-5</v>
+        <v>0.64946494649464903</v>
+      </c>
+      <c r="E12">
+        <v>1.39820925278311E-4</v>
       </c>
       <c r="F12">
         <f t="shared" si="2"/>
-        <v>7.7919909985649227E-9</v>
+        <v>1.9549891145683028E-8</v>
       </c>
       <c r="G12">
-        <v>1021680</v>
+        <v>794376</v>
       </c>
       <c r="H12">
-        <v>3157</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.4">
+        <v>2651</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>16</v>
       </c>
@@ -3511,14 +3477,14 @@
         <v>0.23137821315975901</v>
       </c>
       <c r="D13">
-        <v>0.64920649206491998</v>
+        <v>0.64976497649764897</v>
       </c>
       <c r="E13">
-        <v>3.9827535500713802E-4</v>
+        <v>1.60209077721962E-4</v>
       </c>
       <c r="F13">
         <f t="shared" si="2"/>
-        <v>1.5862325840606181E-7</v>
+        <v>2.5666948584521662E-8</v>
       </c>
       <c r="G13">
         <v>2134656</v>
@@ -3527,7 +3493,7 @@
         <v>3216</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>22</v>
       </c>
@@ -3538,23 +3504,23 @@
         <v>0.25795382990710702</v>
       </c>
       <c r="D14">
-        <v>0.64952649526495199</v>
-      </c>
-      <c r="E14" s="1">
-        <v>7.8272154975134097E-5</v>
+        <v>0.64936493649364901</v>
+      </c>
+      <c r="E14">
+        <v>2.39830926278439E-4</v>
       </c>
       <c r="F14">
         <f t="shared" si="2"/>
-        <v>6.1265302444514098E-9</v>
+        <v>5.7518873199574041E-8</v>
       </c>
       <c r="G14">
-        <v>5486052</v>
+        <v>4936536</v>
       </c>
       <c r="H14">
-        <v>3982</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.4">
+        <v>3762</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>32</v>
       </c>
@@ -3565,14 +3531,14 @@
         <v>0.28922276644969802</v>
       </c>
       <c r="D15">
-        <v>0.65002650026500197</v>
-      </c>
-      <c r="E15">
-        <v>4.2173284507485099E-4</v>
+        <v>0.64956495649564905</v>
+      </c>
+      <c r="E15" s="1">
+        <v>3.9810924278183002E-5</v>
       </c>
       <c r="F15">
         <f t="shared" si="2"/>
-        <v>1.7785859261492827E-7</v>
+        <v>1.5849096918832207E-9</v>
       </c>
       <c r="G15">
         <v>13330944</v>
@@ -3581,7 +3547,7 @@
         <v>4512</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>45</v>
       </c>
@@ -3592,20 +3558,20 @@
         <v>0.31767378909116201</v>
       </c>
       <c r="D16">
-        <v>0.64973649736497296</v>
-      </c>
-      <c r="E16">
-        <v>1.3172994504584399E-4</v>
+        <v>0.64956495649564905</v>
+      </c>
+      <c r="E16" s="1">
+        <v>3.9810924278183002E-5</v>
       </c>
       <c r="F16">
         <f t="shared" si="2"/>
-        <v>1.7352778421781077E-8</v>
+        <v>1.5849096918832207E-9</v>
       </c>
       <c r="G16">
-        <v>34428240</v>
+        <v>32900580</v>
       </c>
       <c r="H16">
-        <v>5535</v>
+        <v>5355</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.4">
@@ -3619,14 +3585,14 @@
         <v>0.347067319739638</v>
       </c>
       <c r="D17">
-        <v>0.64942649426494203</v>
+        <v>0.64996499649965001</v>
       </c>
       <c r="E17">
-        <v>1.7827315498519699E-4</v>
+        <v>3.6022907972221803E-4</v>
       </c>
       <c r="F17">
         <f t="shared" si="2"/>
-        <v>3.1781317788376065E-8</v>
+        <v>1.2976498987751611E-7</v>
       </c>
       <c r="G17">
         <v>83566080</v>
@@ -3646,17 +3612,17 @@
         <v>0.37551834238110199</v>
       </c>
       <c r="D18">
-        <v>0.64946649466494599</v>
-      </c>
-      <c r="E18">
-        <v>1.3827275498112801E-4</v>
+        <v>0.64956495649564905</v>
+      </c>
+      <c r="E18" s="1">
+        <v>3.9810924278183002E-5</v>
       </c>
       <c r="F18">
         <f t="shared" si="2"/>
-        <v>1.9119354770071062E-8</v>
+        <v>1.5849096918832207E-9</v>
       </c>
       <c r="G18">
-        <v>210073500</v>
+        <v>205896600</v>
       </c>
       <c r="H18">
         <v>7650</v>
@@ -3673,14 +3639,14 @@
         <v>0.40491187302957798</v>
       </c>
       <c r="D19">
-        <v>0.64950649506494995</v>
+        <v>0.64956495649564905</v>
       </c>
       <c r="E19" s="1">
-        <v>9.8272354977169102E-5</v>
+        <v>3.9810924278183002E-5</v>
       </c>
       <c r="F19">
         <f t="shared" si="2"/>
-        <v>9.6574557527587323E-9</v>
+        <v>1.5849096918832207E-9</v>
       </c>
       <c r="G19">
         <v>520722432</v>
@@ -3700,20 +3666,20 @@
         <v>0.173533659869819</v>
       </c>
       <c r="D20">
-        <v>0.64938649386493796</v>
-      </c>
-      <c r="E20">
-        <v>2.1827355498915601E-4</v>
+        <v>0.64966496649664895</v>
+      </c>
+      <c r="E20" s="1">
+        <v>6.0199076721945099E-5</v>
       </c>
       <c r="F20">
         <f t="shared" si="2"/>
-        <v>4.7643344807604109E-8</v>
+        <v>3.6239288381746321E-9</v>
       </c>
       <c r="G20">
-        <v>516240</v>
+        <v>354240</v>
       </c>
       <c r="H20">
-        <v>3000</v>
+        <v>2264</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.4">
@@ -3727,20 +3693,20 @@
         <v>0.20010927661716699</v>
       </c>
       <c r="D21">
-        <v>0.64984649846498399</v>
-      </c>
-      <c r="E21">
-        <v>2.4173104505686901E-4</v>
+        <v>0.64966496649664895</v>
+      </c>
+      <c r="E21" s="1">
+        <v>6.0199076721945099E-5</v>
       </c>
       <c r="F21">
         <f t="shared" si="2"/>
-        <v>5.8433898144286034E-8</v>
+        <v>3.6239288381746321E-9</v>
       </c>
       <c r="G21">
-        <v>1021680</v>
+        <v>794376</v>
       </c>
       <c r="H21">
-        <v>3157</v>
+        <v>2651</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.4">
@@ -3754,14 +3720,14 @@
         <v>0.23137821315975901</v>
       </c>
       <c r="D22">
-        <v>0.65001650016500101</v>
+        <v>0.64986498649864899</v>
       </c>
       <c r="E22">
-        <v>4.1173274507388897E-4</v>
+        <v>2.6021907872209E-4</v>
       </c>
       <c r="F22">
         <f t="shared" si="2"/>
-        <v>1.6952385336608004E-7</v>
+        <v>6.7713968930973274E-8</v>
       </c>
       <c r="G22">
         <v>2134656</v>
@@ -3781,20 +3747,20 @@
         <v>0.25795382990710702</v>
       </c>
       <c r="D23">
-        <v>0.64910649106491003</v>
+        <v>0.64996499649965001</v>
       </c>
       <c r="E23">
-        <v>4.9827635501720202E-4</v>
+        <v>3.6022907972221803E-4</v>
       </c>
       <c r="F23">
         <f t="shared" si="2"/>
-        <v>2.4827932596922876E-7</v>
+        <v>1.2976498987751611E-7</v>
       </c>
       <c r="G23">
-        <v>5486052</v>
+        <v>4936536</v>
       </c>
       <c r="H23">
-        <v>3982</v>
+        <v>3762</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.4">
@@ -3808,14 +3774,14 @@
         <v>0.28922276644969802</v>
       </c>
       <c r="D24">
-        <v>0.64980649806498003</v>
-      </c>
-      <c r="E24">
-        <v>2.017306450528E-4</v>
+        <v>0.64956495649564905</v>
+      </c>
+      <c r="E24" s="1">
+        <v>3.9810924278183002E-5</v>
       </c>
       <c r="F24">
         <f t="shared" si="2"/>
-        <v>4.0695253153418782E-8</v>
+        <v>1.5849096918832207E-9</v>
       </c>
       <c r="G24">
         <v>13330944</v>
@@ -3835,20 +3801,20 @@
         <v>0.31767378909116201</v>
       </c>
       <c r="D25">
-        <v>0.65005650056500497</v>
-      </c>
-      <c r="E25">
-        <v>4.5173314507784802E-4</v>
+        <v>0.64966496649664895</v>
+      </c>
+      <c r="E25" s="1">
+        <v>6.0199076721945099E-5</v>
       </c>
       <c r="F25">
         <f t="shared" si="2"/>
-        <v>2.0406283436192407E-7</v>
+        <v>3.6239288381746321E-9</v>
       </c>
       <c r="G25">
-        <v>34428240</v>
+        <v>32900580</v>
       </c>
       <c r="H25">
-        <v>5535</v>
+        <v>5355</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.4">
@@ -3862,14 +3828,14 @@
         <v>0.347067319739638</v>
       </c>
       <c r="D26">
-        <v>0.65002650026500197</v>
+        <v>0.65016501650165004</v>
       </c>
       <c r="E26">
-        <v>4.2173284507485099E-4</v>
+        <v>5.60249081722363E-4</v>
       </c>
       <c r="F26">
         <f t="shared" si="2"/>
-        <v>1.7785859261492827E-7</v>
+        <v>3.1387903357075096E-7</v>
       </c>
       <c r="G26">
         <v>83566080</v>
@@ -3889,17 +3855,17 @@
         <v>0.37551834238110199</v>
       </c>
       <c r="D27">
-        <v>0.64942649426494203</v>
+        <v>0.64946494649464903</v>
       </c>
       <c r="E27">
-        <v>1.7827315498519699E-4</v>
+        <v>1.39820925278311E-4</v>
       </c>
       <c r="F27">
         <f t="shared" si="2"/>
-        <v>3.1781317788376065E-8</v>
+        <v>1.9549891145683028E-8</v>
       </c>
       <c r="G27">
-        <v>210073500</v>
+        <v>205896600</v>
       </c>
       <c r="H27">
         <v>7650</v>
@@ -3916,14 +3882,14 @@
         <v>0.40491187302957798</v>
       </c>
       <c r="D28">
-        <v>0.64951649516495102</v>
+        <v>0.64966496649664895</v>
       </c>
       <c r="E28" s="1">
-        <v>8.8272254976096102E-5</v>
+        <v>6.0199076721945099E-5</v>
       </c>
       <c r="F28">
         <f t="shared" si="2"/>
-        <v>7.7919909985649227E-9</v>
+        <v>3.6239288381746321E-9</v>
       </c>
       <c r="G28">
         <v>520722432</v>
@@ -3943,20 +3909,20 @@
         <v>0.173533659869819</v>
       </c>
       <c r="D29">
-        <v>0.64963649636496301</v>
-      </c>
-      <c r="E29" s="1">
-        <v>3.17289450358915E-5</v>
+        <v>0.649264926492649</v>
+      </c>
+      <c r="E29">
+        <v>3.39840927278456E-4</v>
       </c>
       <c r="F29">
         <f t="shared" si="2"/>
-        <v>1.0067259530906239E-9</v>
+        <v>1.1549185585348082E-7</v>
       </c>
       <c r="G29">
-        <v>516240</v>
+        <v>354240</v>
       </c>
       <c r="H29">
-        <v>3000</v>
+        <v>2264</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.4">
@@ -3970,20 +3936,20 @@
         <v>0.20010927661716699</v>
       </c>
       <c r="D30">
-        <v>0.64914649146491399</v>
+        <v>0.64946494649464903</v>
       </c>
       <c r="E30">
-        <v>4.5827595501313201E-4</v>
+        <v>1.39820925278311E-4</v>
       </c>
       <c r="F30">
         <f t="shared" si="2"/>
-        <v>2.1001685094319819E-7</v>
+        <v>1.9549891145683028E-8</v>
       </c>
       <c r="G30">
-        <v>1021680</v>
+        <v>794376</v>
       </c>
       <c r="H30">
-        <v>3157</v>
+        <v>2651</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.4">
@@ -3997,14 +3963,14 @@
         <v>0.23137821315975901</v>
       </c>
       <c r="D31">
-        <v>0.64927649276492705</v>
-      </c>
-      <c r="E31">
-        <v>3.28274655000182E-4</v>
+        <v>0.64966496649664895</v>
+      </c>
+      <c r="E31" s="1">
+        <v>6.0199076721945099E-5</v>
       </c>
       <c r="F31">
         <f t="shared" si="2"/>
-        <v>1.0776424911548852E-7</v>
+        <v>3.6239288381746321E-9</v>
       </c>
       <c r="G31">
         <v>2134656</v>
@@ -4024,20 +3990,20 @@
         <v>0.25795382990710702</v>
       </c>
       <c r="D32">
-        <v>0.64920649206491998</v>
+        <v>0.64946494649464903</v>
       </c>
       <c r="E32">
-        <v>3.9827535500713802E-4</v>
+        <v>1.39820925278311E-4</v>
       </c>
       <c r="F32">
         <f t="shared" si="2"/>
-        <v>1.5862325840606181E-7</v>
+        <v>1.9549891145683028E-8</v>
       </c>
       <c r="G32">
-        <v>5486052</v>
+        <v>4936536</v>
       </c>
       <c r="H32">
-        <v>3982</v>
+        <v>3762</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.4">
@@ -4051,14 +4017,14 @@
         <v>0.28922276644969802</v>
       </c>
       <c r="D33">
-        <v>0.64912649126491195</v>
+        <v>0.64996499649965001</v>
       </c>
       <c r="E33">
-        <v>4.7827615501516702E-4</v>
+        <v>3.6022907972221803E-4</v>
       </c>
       <c r="F33">
         <f t="shared" si="2"/>
-        <v>2.2874808045609207E-7</v>
+        <v>1.2976498987751611E-7</v>
       </c>
       <c r="G33">
         <v>13330944</v>
@@ -4078,20 +4044,20 @@
         <v>0.31767378909116201</v>
       </c>
       <c r="D34">
-        <v>0.64956649566495595</v>
-      </c>
-      <c r="E34" s="1">
-        <v>3.8271754971175298E-5</v>
+        <v>0.64986498649864899</v>
+      </c>
+      <c r="E34">
+        <v>2.6021907872209E-4</v>
       </c>
       <c r="F34">
         <f t="shared" si="2"/>
-        <v>1.4647272285736811E-9</v>
+        <v>6.7713968930973274E-8</v>
       </c>
       <c r="G34">
-        <v>34428240</v>
+        <v>32900580</v>
       </c>
       <c r="H34">
-        <v>5535</v>
+        <v>5355</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.4">
@@ -4105,14 +4071,14 @@
         <v>0.347067319739638</v>
       </c>
       <c r="D35">
-        <v>0.64909649096490896</v>
+        <v>0.64976497649764897</v>
       </c>
       <c r="E35">
-        <v>5.0827645501816399E-4</v>
+        <v>1.60209077721962E-4</v>
       </c>
       <c r="F35">
         <f t="shared" si="2"/>
-        <v>2.5834495472583168E-7</v>
+        <v>2.5666948584521662E-8</v>
       </c>
       <c r="G35">
         <v>83566080</v>
@@ -4132,17 +4098,17 @@
         <v>0.37551834238110199</v>
       </c>
       <c r="D36">
-        <v>0.64973649736497296</v>
+        <v>0.64916491649164898</v>
       </c>
       <c r="E36">
-        <v>1.3172994504584399E-4</v>
+        <v>4.3985092827858398E-4</v>
       </c>
       <c r="F36">
         <f t="shared" si="2"/>
-        <v>1.7352778421781077E-8</v>
+        <v>1.9346883910753202E-7</v>
       </c>
       <c r="G36">
-        <v>210073500</v>
+        <v>205896600</v>
       </c>
       <c r="H36">
         <v>7650</v>
@@ -4159,14 +4125,14 @@
         <v>0.40491187302957798</v>
       </c>
       <c r="D37">
-        <v>0.649436494364943</v>
-      </c>
-      <c r="E37">
-        <v>1.68273054984124E-4</v>
+        <v>0.64956495649564905</v>
+      </c>
+      <c r="E37" s="1">
+        <v>3.9810924278183002E-5</v>
       </c>
       <c r="F37">
         <f t="shared" si="2"/>
-        <v>2.831582103369002E-8</v>
+        <v>1.5849096918832207E-9</v>
       </c>
       <c r="G37">
         <v>520722432</v>
@@ -4186,20 +4152,20 @@
         <v>0.173533659869819</v>
       </c>
       <c r="D38">
-        <v>0.65100651006510002</v>
+        <v>0.64936493649364901</v>
       </c>
       <c r="E38">
-        <v>1.40174264517289E-3</v>
+        <v>2.39830926278439E-4</v>
       </c>
       <c r="F38">
         <f t="shared" si="2"/>
-        <v>1.9648824432962908E-6</v>
+        <v>5.7518873199574041E-8</v>
       </c>
       <c r="G38">
-        <v>516240</v>
+        <v>354240</v>
       </c>
       <c r="H38">
-        <v>3000</v>
+        <v>2264</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.4">
@@ -4213,20 +4179,20 @@
         <v>0.20010927661716699</v>
       </c>
       <c r="D39">
-        <v>0.64841648416484099</v>
+        <v>0.65016501650165004</v>
       </c>
       <c r="E39">
-        <v>1.18828325508613E-3</v>
+        <v>5.60249081722363E-4</v>
       </c>
       <c r="F39">
         <f t="shared" si="2"/>
-        <v>1.4120170943180888E-6</v>
+        <v>3.1387903357075096E-7</v>
       </c>
       <c r="G39">
-        <v>1021680</v>
+        <v>794376</v>
       </c>
       <c r="H39">
-        <v>3157</v>
+        <v>2651</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.4">
@@ -4240,14 +4206,14 @@
         <v>0.23137821315975901</v>
       </c>
       <c r="D40">
-        <v>0.64915649156491495</v>
+        <v>0.649264926492649</v>
       </c>
       <c r="E40">
-        <v>4.4827585501216999E-4</v>
+        <v>3.39840927278456E-4</v>
       </c>
       <c r="F40">
         <f t="shared" si="2"/>
-        <v>2.0095124218689206E-7</v>
+        <v>1.1549185585348082E-7</v>
       </c>
       <c r="G40">
         <v>2134656</v>
@@ -4267,20 +4233,20 @@
         <v>0.25795382990710702</v>
       </c>
       <c r="D41">
-        <v>0.64921649216492106</v>
+        <v>0.65006500650065002</v>
       </c>
       <c r="E41">
-        <v>3.88275255006176E-4</v>
+        <v>4.60239080722346E-4</v>
       </c>
       <c r="F41">
         <f t="shared" si="2"/>
-        <v>1.5075767365011101E-7</v>
+        <v>2.1182001142415012E-7</v>
       </c>
       <c r="G41">
-        <v>5486052</v>
+        <v>4936536</v>
       </c>
       <c r="H41">
-        <v>3982</v>
+        <v>3762</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.4">
@@ -4294,14 +4260,14 @@
         <v>0.28922276644969802</v>
       </c>
       <c r="D42">
-        <v>0.64957649576495702</v>
-      </c>
-      <c r="E42" s="1">
-        <v>2.8271654970102301E-5</v>
+        <v>0.64976497649764897</v>
+      </c>
+      <c r="E42">
+        <v>1.60209077721962E-4</v>
       </c>
       <c r="F42">
         <f t="shared" si="2"/>
-        <v>7.9928647474851016E-10</v>
+        <v>2.5666948584521662E-8</v>
       </c>
       <c r="G42">
         <v>13330944</v>
@@ -4321,20 +4287,20 @@
         <v>0.31767378909116201</v>
       </c>
       <c r="D43">
-        <v>0.64940649406494</v>
+        <v>0.649264926492649</v>
       </c>
       <c r="E43">
-        <v>1.98273354987121E-4</v>
+        <v>3.39840927278456E-4</v>
       </c>
       <c r="F43">
         <f t="shared" si="2"/>
-        <v>3.9312323297848901E-8</v>
+        <v>1.1549185585348082E-7</v>
       </c>
       <c r="G43">
-        <v>34428240</v>
+        <v>32900580</v>
       </c>
       <c r="H43">
-        <v>5535</v>
+        <v>5355</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.4">
@@ -4348,14 +4314,14 @@
         <v>0.347067319739638</v>
       </c>
       <c r="D44">
-        <v>0.64984649846498399</v>
-      </c>
-      <c r="E44">
-        <v>2.4173104505686901E-4</v>
+        <v>0.64956495649564905</v>
+      </c>
+      <c r="E44" s="1">
+        <v>3.9810924278183002E-5</v>
       </c>
       <c r="F44">
         <f t="shared" si="2"/>
-        <v>5.8433898144286034E-8</v>
+        <v>1.5849096918832207E-9</v>
       </c>
       <c r="G44">
         <v>83566080</v>
@@ -4375,17 +4341,17 @@
         <v>0.37551834238110199</v>
       </c>
       <c r="D45">
-        <v>0.64891648916489097</v>
+        <v>0.649264926492649</v>
       </c>
       <c r="E45">
-        <v>6.8827825503614505E-4</v>
+        <v>3.39840927278456E-4</v>
       </c>
       <c r="F45">
         <f t="shared" si="2"/>
-        <v>4.737269563556007E-7</v>
+        <v>1.1549185585348082E-7</v>
       </c>
       <c r="G45">
-        <v>210073500</v>
+        <v>205896600</v>
       </c>
       <c r="H45">
         <v>7650</v>
@@ -4402,14 +4368,14 @@
         <v>0.40491187302957798</v>
       </c>
       <c r="D46">
-        <v>0.649346493464934</v>
-      </c>
-      <c r="E46">
-        <v>2.5827395499311502E-4</v>
+        <v>0.64956495649564905</v>
+      </c>
+      <c r="E46" s="1">
+        <v>3.9810924278183002E-5</v>
       </c>
       <c r="F46">
         <f t="shared" si="2"/>
-        <v>6.670543582778561E-8</v>
+        <v>1.5849096918832207E-9</v>
       </c>
       <c r="G46">
         <v>520722432</v>
@@ -4429,20 +4395,20 @@
         <v>0.173533659869819</v>
       </c>
       <c r="D47">
-        <v>0.64955649556495498</v>
-      </c>
-      <c r="E47" s="1">
-        <v>4.8271854972137202E-5</v>
+        <v>0.64936493649364901</v>
+      </c>
+      <c r="E47">
+        <v>2.39830926278439E-4</v>
       </c>
       <c r="F47">
         <f t="shared" si="2"/>
-        <v>2.3301719824510472E-9</v>
+        <v>5.7518873199574041E-8</v>
       </c>
       <c r="G47">
-        <v>516240</v>
+        <v>354240</v>
       </c>
       <c r="H47">
-        <v>3000</v>
+        <v>2264</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.4">
@@ -4456,20 +4422,20 @@
         <v>0.20010927661716699</v>
       </c>
       <c r="D48">
-        <v>0.64977649776497703</v>
+        <v>0.64996499649965001</v>
       </c>
       <c r="E48">
-        <v>1.71730345049803E-4</v>
+        <v>3.6022907972221803E-4</v>
       </c>
       <c r="F48">
         <f t="shared" si="2"/>
-        <v>2.9491311410924398E-8</v>
+        <v>1.2976498987751611E-7</v>
       </c>
       <c r="G48">
-        <v>1021680</v>
+        <v>794376</v>
       </c>
       <c r="H48">
-        <v>3157</v>
+        <v>2651</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.4">
@@ -4483,14 +4449,14 @@
         <v>0.23137821315975901</v>
       </c>
       <c r="D49">
-        <v>0.64964649646496397</v>
+        <v>0.64956495649564905</v>
       </c>
       <c r="E49" s="1">
-        <v>4.1729045036853397E-5</v>
+        <v>3.9810924278183002E-5</v>
       </c>
       <c r="F49">
         <f t="shared" si="2"/>
-        <v>1.7413131996877392E-9</v>
+        <v>1.5849096918832207E-9</v>
       </c>
       <c r="G49">
         <v>2134656</v>
@@ -4510,20 +4476,20 @@
         <v>0.25795382990710702</v>
       </c>
       <c r="D50">
-        <v>0.64960649606496002</v>
-      </c>
-      <c r="E50" s="1">
-        <v>1.7286450328945999E-6</v>
+        <v>0.64976497649764897</v>
+      </c>
+      <c r="E50">
+        <v>1.60209077721962E-4</v>
       </c>
       <c r="F50">
         <f t="shared" si="2"/>
-        <v>2.9882136497511725E-12</v>
+        <v>2.5666948584521662E-8</v>
       </c>
       <c r="G50">
-        <v>5486052</v>
+        <v>4936536</v>
       </c>
       <c r="H50">
-        <v>3982</v>
+        <v>3762</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.4">
@@ -4537,14 +4503,14 @@
         <v>0.28922276644969802</v>
       </c>
       <c r="D51">
-        <v>0.649026490264902</v>
-      </c>
-      <c r="E51">
-        <v>5.7827715502511902E-4</v>
+        <v>0.64956495649564905</v>
+      </c>
+      <c r="E51" s="1">
+        <v>3.9810924278183002E-5</v>
       </c>
       <c r="F51">
         <f t="shared" si="2"/>
-        <v>3.3440446802394555E-7</v>
+        <v>1.5849096918832207E-9</v>
       </c>
       <c r="G51">
         <v>13330944</v>
@@ -4564,20 +4530,20 @@
         <v>0.31767378909116201</v>
       </c>
       <c r="D52">
-        <v>0.64974649746497404</v>
+        <v>0.64976497649764897</v>
       </c>
       <c r="E52">
-        <v>1.4173004504680601E-4</v>
+        <v>1.60209077721962E-4</v>
       </c>
       <c r="F52">
         <f t="shared" si="2"/>
-        <v>2.0087405668969661E-8</v>
+        <v>2.5666948584521662E-8</v>
       </c>
       <c r="G52">
-        <v>34428240</v>
+        <v>32900580</v>
       </c>
       <c r="H52">
-        <v>5535</v>
+        <v>5355</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.4">
@@ -4591,14 +4557,14 @@
         <v>0.347067319739638</v>
       </c>
       <c r="D53">
-        <v>0.64983649836498303</v>
-      </c>
-      <c r="E53">
-        <v>2.31730945055796E-4</v>
+        <v>0.64966496649664895</v>
+      </c>
+      <c r="E53" s="1">
+        <v>6.0199076721945099E-5</v>
       </c>
       <c r="F53">
         <f t="shared" si="2"/>
-        <v>5.3699230896452341E-8</v>
+        <v>3.6239288381746321E-9</v>
       </c>
       <c r="G53">
         <v>83566080</v>
@@ -4618,17 +4584,17 @@
         <v>0.37551834238110199</v>
       </c>
       <c r="D54">
-        <v>0.64970649706496997</v>
+        <v>0.64976497649764897</v>
       </c>
       <c r="E54">
-        <v>1.01729645042847E-4</v>
+        <v>1.60209077721962E-4</v>
       </c>
       <c r="F54">
         <f t="shared" si="2"/>
-        <v>1.0348920680543647E-8</v>
+        <v>2.5666948584521662E-8</v>
       </c>
       <c r="G54">
-        <v>210073500</v>
+        <v>205896600</v>
       </c>
       <c r="H54">
         <v>7650</v>
@@ -4645,14 +4611,14 @@
         <v>0.40491187302957798</v>
       </c>
       <c r="D55">
-        <v>0.65010650106501</v>
+        <v>0.64986498649864899</v>
       </c>
       <c r="E55">
-        <v>5.0173364508287999E-4</v>
+        <v>2.6021907872209E-4</v>
       </c>
       <c r="F55">
         <f t="shared" si="2"/>
-        <v>2.5173665060815338E-7</v>
+        <v>6.7713968930973274E-8</v>
       </c>
       <c r="G55">
         <v>520722432</v>
@@ -4672,20 +4638,20 @@
         <v>0.173533659869819</v>
       </c>
       <c r="D56">
-        <v>0.64901649016490104</v>
+        <v>0.65016501650165004</v>
       </c>
       <c r="E56">
-        <v>5.8827725502619201E-4</v>
+        <v>5.60249081722363E-4</v>
       </c>
       <c r="F56">
         <f t="shared" si="2"/>
-        <v>3.4607012878115138E-7</v>
+        <v>3.1387903357075096E-7</v>
       </c>
       <c r="G56">
-        <v>516240</v>
+        <v>354240</v>
       </c>
       <c r="H56">
-        <v>3000</v>
+        <v>2264</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.4">
@@ -4699,20 +4665,20 @@
         <v>0.20010927661716699</v>
       </c>
       <c r="D57">
-        <v>0.64928649286492801</v>
+        <v>0.65016501650165004</v>
       </c>
       <c r="E57">
-        <v>3.1827455499910902E-4</v>
+        <v>5.60249081722363E-4</v>
       </c>
       <c r="F57">
         <f t="shared" si="2"/>
-        <v>1.0129869235988087E-7</v>
+        <v>3.1387903357075096E-7</v>
       </c>
       <c r="G57">
-        <v>1021680</v>
+        <v>794376</v>
       </c>
       <c r="H57">
-        <v>3157</v>
+        <v>2651</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.4">
@@ -4726,14 +4692,14 @@
         <v>0.23137821315975901</v>
       </c>
       <c r="D58">
-        <v>0.64993649936499298</v>
-      </c>
-      <c r="E58">
-        <v>3.3173194506585997E-4</v>
+        <v>0.64966496649664895</v>
+      </c>
+      <c r="E58" s="1">
+        <v>6.0199076721945099E-5</v>
       </c>
       <c r="F58">
         <f t="shared" si="2"/>
-        <v>1.1004608337717874E-7</v>
+        <v>3.6239288381746321E-9</v>
       </c>
       <c r="G58">
         <v>2134656</v>
@@ -4753,20 +4719,20 @@
         <v>0.25795382990710702</v>
       </c>
       <c r="D59">
-        <v>0.64981649816498099</v>
+        <v>0.64976497649764897</v>
       </c>
       <c r="E59">
-        <v>2.1173074505387299E-4</v>
+        <v>1.60209077721962E-4</v>
       </c>
       <c r="F59">
         <f t="shared" si="2"/>
-        <v>4.4829908401068164E-8</v>
+        <v>2.5666948584521662E-8</v>
       </c>
       <c r="G59">
-        <v>5486052</v>
+        <v>4936536</v>
       </c>
       <c r="H59">
-        <v>3982</v>
+        <v>3762</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.4">
@@ -4780,14 +4746,14 @@
         <v>0.28922276644969802</v>
       </c>
       <c r="D60">
-        <v>0.64924649246492405</v>
+        <v>0.64936493649364901</v>
       </c>
       <c r="E60">
-        <v>3.5827495500317897E-4</v>
+        <v>2.39830926278439E-4</v>
       </c>
       <c r="F60">
         <f t="shared" si="2"/>
-        <v>1.2836094338252992E-7</v>
+        <v>5.7518873199574041E-8</v>
       </c>
       <c r="G60">
         <v>13330944</v>
@@ -4807,20 +4773,20 @@
         <v>0.31767378909116201</v>
       </c>
       <c r="D61">
-        <v>0.64993649936499298</v>
+        <v>0.64976497649764897</v>
       </c>
       <c r="E61">
-        <v>3.3173194506585997E-4</v>
+        <v>1.60209077721962E-4</v>
       </c>
       <c r="F61">
         <f t="shared" si="2"/>
-        <v>1.1004608337717874E-7</v>
+        <v>2.5666948584521662E-8</v>
       </c>
       <c r="G61">
-        <v>34428240</v>
+        <v>32900580</v>
       </c>
       <c r="H61">
-        <v>5535</v>
+        <v>5355</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.4">
@@ -4834,14 +4800,14 @@
         <v>0.347067319739638</v>
       </c>
       <c r="D62">
-        <v>0.64990649906498998</v>
+        <v>0.64986498649864899</v>
       </c>
       <c r="E62">
-        <v>3.01731645062863E-4</v>
+        <v>2.6021907872209E-4</v>
       </c>
       <c r="F62">
         <f t="shared" si="2"/>
-        <v>9.1041985632341542E-8</v>
+        <v>6.7713968930973274E-8</v>
       </c>
       <c r="G62">
         <v>83566080</v>
@@ -4861,17 +4827,17 @@
         <v>0.37551834238110199</v>
       </c>
       <c r="D63">
-        <v>0.64948649486494803</v>
+        <v>0.64996499649965001</v>
       </c>
       <c r="E63">
-        <v>1.18272554979093E-4</v>
+        <v>3.6022907972221803E-4</v>
       </c>
       <c r="F63">
         <f t="shared" si="2"/>
-        <v>1.3988397261282577E-8</v>
+        <v>1.2976498987751611E-7</v>
       </c>
       <c r="G63">
-        <v>210073500</v>
+        <v>205896600</v>
       </c>
       <c r="H63">
         <v>7650</v>
@@ -4888,14 +4854,14 @@
         <v>0.40491187302957798</v>
       </c>
       <c r="D64">
-        <v>0.64990649906498998</v>
+        <v>0.65016501650165004</v>
       </c>
       <c r="E64">
-        <v>3.01731645062863E-4</v>
+        <v>5.60249081722363E-4</v>
       </c>
       <c r="F64">
         <f t="shared" si="2"/>
-        <v>9.1041985632341542E-8</v>
+        <v>3.1387903357075096E-7</v>
       </c>
       <c r="G64">
         <v>520722432</v>
@@ -4915,20 +4881,20 @@
         <v>0.173533659869819</v>
       </c>
       <c r="D65">
-        <v>0.64935649356493497</v>
-      </c>
-      <c r="E65">
-        <v>2.48273854992153E-4</v>
+        <v>0.64966496649664895</v>
+      </c>
+      <c r="E65" s="1">
+        <v>6.0199076721945099E-5</v>
       </c>
       <c r="F65">
         <f t="shared" si="2"/>
-        <v>6.1639907072664622E-8</v>
+        <v>3.6239288381746321E-9</v>
       </c>
       <c r="G65">
-        <v>516240</v>
+        <v>354240</v>
       </c>
       <c r="H65">
-        <v>3000</v>
+        <v>2264</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.4">
@@ -4942,20 +4908,20 @@
         <v>0.20010927661716699</v>
       </c>
       <c r="D66">
-        <v>0.64987649876498699</v>
+        <v>0.65026502650264995</v>
       </c>
       <c r="E66">
-        <v>2.7173134505986598E-4</v>
+        <v>6.6025908272249103E-4</v>
       </c>
       <c r="F66">
         <f t="shared" si="2"/>
-        <v>7.3837923888043954E-8</v>
+        <v>4.3594205631754526E-7</v>
       </c>
       <c r="G66">
-        <v>1021680</v>
+        <v>794376</v>
       </c>
       <c r="H66">
-        <v>3157</v>
+        <v>2651</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.4">
@@ -4969,14 +4935,14 @@
         <v>0.23137821315975901</v>
       </c>
       <c r="D67">
-        <v>0.65027650276502702</v>
+        <v>0.64936493649364901</v>
       </c>
       <c r="E67">
-        <v>6.7173534509989898E-4</v>
+        <v>2.39830926278439E-4</v>
       </c>
       <c r="F67">
-        <f t="shared" ref="F67:F130" si="4">E67*E67</f>
-        <v>4.5122837385648035E-7</v>
+        <f t="shared" ref="F67:F91" si="4">E67*E67</f>
+        <v>5.7518873199574041E-8</v>
       </c>
       <c r="G67">
         <v>2134656</v>
@@ -4996,20 +4962,20 @@
         <v>0.25795382990710702</v>
       </c>
       <c r="D68">
-        <v>0.64885648856488498</v>
+        <v>0.64936493649364901</v>
       </c>
       <c r="E68">
-        <v>7.4827885504213899E-4</v>
+        <v>2.39830926278439E-4</v>
       </c>
       <c r="F68">
         <f t="shared" si="4"/>
-        <v>5.5992124490317441E-7</v>
+        <v>5.7518873199574041E-8</v>
       </c>
       <c r="G68">
-        <v>5486052</v>
+        <v>4936536</v>
       </c>
       <c r="H68">
-        <v>3982</v>
+        <v>3762</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.4">
@@ -5023,14 +4989,14 @@
         <v>0.28922276644969802</v>
       </c>
       <c r="D69">
-        <v>0.65012650126501204</v>
+        <v>0.64986498649864899</v>
       </c>
       <c r="E69">
-        <v>5.2173384508480403E-4</v>
+        <v>2.6021907872209E-4</v>
       </c>
       <c r="F69">
         <f t="shared" si="4"/>
-        <v>2.722062051069743E-7</v>
+        <v>6.7713968930973274E-8</v>
       </c>
       <c r="G69">
         <v>13330944</v>
@@ -5050,20 +5016,20 @@
         <v>0.31767378909116201</v>
       </c>
       <c r="D70">
-        <v>0.64986649866498603</v>
+        <v>0.64946494649464903</v>
       </c>
       <c r="E70">
-        <v>2.6173124505890401E-4</v>
+        <v>1.39820925278311E-4</v>
       </c>
       <c r="F70">
         <f t="shared" si="4"/>
-        <v>6.8503244640084071E-8</v>
+        <v>1.9549891145683028E-8</v>
       </c>
       <c r="G70">
-        <v>34428240</v>
+        <v>32900580</v>
       </c>
       <c r="H70">
-        <v>5535</v>
+        <v>5355</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.4">
@@ -5077,14 +5043,14 @@
         <v>0.347067319739638</v>
       </c>
       <c r="D71">
-        <v>0.64920649206491998</v>
+        <v>0.64976497649764897</v>
       </c>
       <c r="E71">
-        <v>3.9827535500713802E-4</v>
+        <v>1.60209077721962E-4</v>
       </c>
       <c r="F71">
         <f t="shared" si="4"/>
-        <v>1.5862325840606181E-7</v>
+        <v>2.5666948584521662E-8</v>
       </c>
       <c r="G71">
         <v>83566080</v>
@@ -5104,17 +5070,17 @@
         <v>0.37551834238110199</v>
       </c>
       <c r="D72">
-        <v>0.64945649456494503</v>
+        <v>0.64976497649764897</v>
       </c>
       <c r="E72">
-        <v>1.48272854982201E-4</v>
+        <v>1.60209077721962E-4</v>
       </c>
       <c r="F72">
         <f t="shared" si="4"/>
-        <v>2.1984839524572808E-8</v>
+        <v>2.5666948584521662E-8</v>
       </c>
       <c r="G72">
-        <v>210073500</v>
+        <v>205896600</v>
       </c>
       <c r="H72">
         <v>7650</v>
@@ -5131,14 +5097,14 @@
         <v>0.40491187302957798</v>
       </c>
       <c r="D73">
-        <v>0.64882648826488198</v>
-      </c>
-      <c r="E73">
-        <v>7.7827915504513601E-4</v>
+        <v>0.64966496649664895</v>
+      </c>
+      <c r="E73" s="1">
+        <v>6.0199076721945099E-5</v>
       </c>
       <c r="F73">
         <f t="shared" si="4"/>
-        <v>6.057184431777709E-7</v>
+        <v>3.6239288381746321E-9</v>
       </c>
       <c r="G73">
         <v>520722432</v>
@@ -5158,20 +5124,20 @@
         <v>0.173533659869819</v>
       </c>
       <c r="D74">
-        <v>0.64933649336493304</v>
-      </c>
-      <c r="E74">
-        <v>2.6827405499418801E-4</v>
+        <v>0.64966496649664895</v>
+      </c>
+      <c r="E74" s="1">
+        <v>6.0199076721945099E-5</v>
       </c>
       <c r="F74">
         <f t="shared" si="4"/>
-        <v>7.1970968583024616E-8</v>
+        <v>3.6239288381746321E-9</v>
       </c>
       <c r="G74">
-        <v>516240</v>
+        <v>354240</v>
       </c>
       <c r="H74">
-        <v>3000</v>
+        <v>2264</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.4">
@@ -5185,20 +5151,20 @@
         <v>0.20010927661716699</v>
       </c>
       <c r="D75">
-        <v>0.64991649916499095</v>
+        <v>0.64986498649864899</v>
       </c>
       <c r="E75">
-        <v>3.1173174506382502E-4</v>
+        <v>2.6021907872209E-4</v>
       </c>
       <c r="F75">
         <f t="shared" si="4"/>
-        <v>9.7176680880537601E-8</v>
+        <v>6.7713968930973274E-8</v>
       </c>
       <c r="G75">
-        <v>1021680</v>
+        <v>794376</v>
       </c>
       <c r="H75">
-        <v>3157</v>
+        <v>2651</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.4">
@@ -5212,14 +5178,14 @@
         <v>0.23137821315975901</v>
       </c>
       <c r="D76">
-        <v>0.64956649566495595</v>
-      </c>
-      <c r="E76" s="1">
-        <v>3.8271754971175298E-5</v>
+        <v>0.64986498649864899</v>
+      </c>
+      <c r="E76">
+        <v>2.6021907872209E-4</v>
       </c>
       <c r="F76">
         <f t="shared" si="4"/>
-        <v>1.4647272285736811E-9</v>
+        <v>6.7713968930973274E-8</v>
       </c>
       <c r="G76">
         <v>2134656</v>
@@ -5239,20 +5205,20 @@
         <v>0.25795382990710702</v>
       </c>
       <c r="D77">
-        <v>0.64966649666496601</v>
+        <v>0.64966496649664895</v>
       </c>
       <c r="E77" s="1">
-        <v>6.1729245038888396E-5</v>
+        <v>6.0199076721945099E-5</v>
       </c>
       <c r="F77">
         <f t="shared" si="4"/>
-        <v>3.8104996930711277E-9</v>
+        <v>3.6239288381746321E-9</v>
       </c>
       <c r="G77">
-        <v>5486052</v>
+        <v>4936536</v>
       </c>
       <c r="H77">
-        <v>3982</v>
+        <v>3762</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.4">
@@ -5266,14 +5232,14 @@
         <v>0.28922276644969802</v>
       </c>
       <c r="D78">
-        <v>0.64992649926499202</v>
-      </c>
-      <c r="E78">
-        <v>3.2173184506489801E-4</v>
+        <v>0.64966496649664895</v>
+      </c>
+      <c r="E78" s="1">
+        <v>6.0199076721945099E-5</v>
       </c>
       <c r="F78">
         <f t="shared" si="4"/>
-        <v>1.0351138012886354E-7</v>
+        <v>3.6239288381746321E-9</v>
       </c>
       <c r="G78">
         <v>13330944</v>
@@ -5293,20 +5259,20 @@
         <v>0.31767378909116201</v>
       </c>
       <c r="D79">
-        <v>0.649436494364943</v>
-      </c>
-      <c r="E79">
-        <v>1.68273054984124E-4</v>
+        <v>0.64966496649664895</v>
+      </c>
+      <c r="E79" s="1">
+        <v>6.0199076721945099E-5</v>
       </c>
       <c r="F79">
         <f t="shared" si="4"/>
-        <v>2.831582103369002E-8</v>
+        <v>3.6239288381746321E-9</v>
       </c>
       <c r="G79">
-        <v>34428240</v>
+        <v>32900580</v>
       </c>
       <c r="H79">
-        <v>5535</v>
+        <v>5355</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.4">
@@ -5320,14 +5286,14 @@
         <v>0.347067319739638</v>
       </c>
       <c r="D80">
-        <v>0.64938649386493796</v>
+        <v>0.64996499649965001</v>
       </c>
       <c r="E80">
-        <v>2.1827355498915601E-4</v>
+        <v>3.6022907972221803E-4</v>
       </c>
       <c r="F80">
         <f t="shared" si="4"/>
-        <v>4.7643344807604109E-8</v>
+        <v>1.2976498987751611E-7</v>
       </c>
       <c r="G80">
         <v>83566080</v>
@@ -5347,17 +5313,17 @@
         <v>0.37551834238110199</v>
       </c>
       <c r="D81">
-        <v>0.64938649386493796</v>
-      </c>
-      <c r="E81">
-        <v>2.1827355498915601E-4</v>
+        <v>0.64966496649664895</v>
+      </c>
+      <c r="E81" s="1">
+        <v>6.0199076721945099E-5</v>
       </c>
       <c r="F81">
         <f t="shared" si="4"/>
-        <v>4.7643344807604109E-8</v>
+        <v>3.6239288381746321E-9</v>
       </c>
       <c r="G81">
-        <v>210073500</v>
+        <v>205896600</v>
       </c>
       <c r="H81">
         <v>7650</v>
@@ -5374,14 +5340,14 @@
         <v>0.40491187302957798</v>
       </c>
       <c r="D82">
-        <v>0.64969649696496901</v>
+        <v>0.64956495649564905</v>
       </c>
       <c r="E82" s="1">
-        <v>9.1729545041885298E-5</v>
+        <v>3.9810924278183002E-5</v>
       </c>
       <c r="F82">
         <f t="shared" si="4"/>
-        <v>8.4143094335912632E-9</v>
+        <v>1.5849096918832207E-9</v>
       </c>
       <c r="G82">
         <v>520722432</v>
@@ -5401,20 +5367,20 @@
         <v>0.173533659869819</v>
       </c>
       <c r="D83">
-        <v>0.64941649416494096</v>
+        <v>0.65006500650065002</v>
       </c>
       <c r="E83">
-        <v>1.8827325498615901E-4</v>
+        <v>4.60239080722346E-4</v>
       </c>
       <c r="F83">
         <f t="shared" si="4"/>
-        <v>3.5446818543083249E-8</v>
+        <v>2.1182001142415012E-7</v>
       </c>
       <c r="G83">
-        <v>516240</v>
+        <v>354240</v>
       </c>
       <c r="H83">
-        <v>3000</v>
+        <v>2264</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.4">
@@ -5428,20 +5394,20 @@
         <v>0.20010927661716699</v>
       </c>
       <c r="D84">
-        <v>0.64925649256492501</v>
+        <v>0.64936493649364901</v>
       </c>
       <c r="E84">
-        <v>3.4827485500210599E-4</v>
+        <v>2.39830926278439E-4</v>
       </c>
       <c r="F84">
         <f t="shared" si="4"/>
-        <v>1.2129537462673795E-7</v>
+        <v>5.7518873199574041E-8</v>
       </c>
       <c r="G84">
-        <v>1021680</v>
+        <v>794376</v>
       </c>
       <c r="H84">
-        <v>3157</v>
+        <v>2651</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.4">
@@ -5455,14 +5421,14 @@
         <v>0.23137821315975901</v>
       </c>
       <c r="D85">
-        <v>0.64963649636496301</v>
-      </c>
-      <c r="E85" s="1">
-        <v>3.17289450358915E-5</v>
+        <v>0.64936493649364901</v>
+      </c>
+      <c r="E85">
+        <v>2.39830926278439E-4</v>
       </c>
       <c r="F85">
         <f t="shared" si="4"/>
-        <v>1.0067259530906239E-9</v>
+        <v>5.7518873199574041E-8</v>
       </c>
       <c r="G85">
         <v>2134656</v>
@@ -5482,20 +5448,20 @@
         <v>0.25795382990710702</v>
       </c>
       <c r="D86">
-        <v>0.64920649206491998</v>
+        <v>0.649264926492649</v>
       </c>
       <c r="E86">
-        <v>3.9827535500713802E-4</v>
+        <v>3.39840927278456E-4</v>
       </c>
       <c r="F86">
         <f t="shared" si="4"/>
-        <v>1.5862325840606181E-7</v>
+        <v>1.1549185585348082E-7</v>
       </c>
       <c r="G86">
-        <v>5486052</v>
+        <v>4936536</v>
       </c>
       <c r="H86">
-        <v>3982</v>
+        <v>3762</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.4">
@@ -5509,14 +5475,14 @@
         <v>0.28922276644969802</v>
       </c>
       <c r="D87">
-        <v>0.64936649366493604</v>
+        <v>0.64916491649164898</v>
       </c>
       <c r="E87">
-        <v>2.3827375499119101E-4</v>
+        <v>4.3985092827858398E-4</v>
       </c>
       <c r="F87">
         <f t="shared" si="4"/>
-        <v>5.6774382317602123E-8</v>
+        <v>1.9346883910753202E-7</v>
       </c>
       <c r="G87">
         <v>13330944</v>
@@ -5536,20 +5502,20 @@
         <v>0.31767378909116201</v>
       </c>
       <c r="D88">
-        <v>0.64990649906498998</v>
+        <v>0.64946494649464903</v>
       </c>
       <c r="E88">
-        <v>3.01731645062863E-4</v>
+        <v>1.39820925278311E-4</v>
       </c>
       <c r="F88">
         <f t="shared" si="4"/>
-        <v>9.1041985632341542E-8</v>
+        <v>1.9549891145683028E-8</v>
       </c>
       <c r="G88">
-        <v>34428240</v>
+        <v>32900580</v>
       </c>
       <c r="H88">
-        <v>5535</v>
+        <v>5355</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.4">
@@ -5563,14 +5529,14 @@
         <v>0.347067319739638</v>
       </c>
       <c r="D89">
-        <v>0.64903649036490296</v>
+        <v>0.64976497649764897</v>
       </c>
       <c r="E89">
-        <v>5.6827705502415695E-4</v>
+        <v>1.60209077721962E-4</v>
       </c>
       <c r="F89">
         <f t="shared" si="4"/>
-        <v>3.229388112669287E-7</v>
+        <v>2.5666948584521662E-8</v>
       </c>
       <c r="G89">
         <v>83566080</v>
@@ -5590,17 +5556,17 @@
         <v>0.37551834238110199</v>
       </c>
       <c r="D90">
-        <v>0.64973649736497296</v>
+        <v>0.64936493649364901</v>
       </c>
       <c r="E90">
-        <v>1.3172994504584399E-4</v>
+        <v>2.39830926278439E-4</v>
       </c>
       <c r="F90">
         <f t="shared" si="4"/>
-        <v>1.7352778421781077E-8</v>
+        <v>5.7518873199574041E-8</v>
       </c>
       <c r="G90">
-        <v>210073500</v>
+        <v>205896600</v>
       </c>
       <c r="H90">
         <v>7650</v>
@@ -5617,14 +5583,14 @@
         <v>0.40491187302957798</v>
       </c>
       <c r="D91">
-        <v>0.64926649266492598</v>
+        <v>0.64986498649864899</v>
       </c>
       <c r="E91">
-        <v>3.3827475500114402E-4</v>
+        <v>2.6021907872209E-4</v>
       </c>
       <c r="F91">
         <f t="shared" si="4"/>
-        <v>1.1442980987108402E-7</v>
+        <v>6.7713968930973274E-8</v>
       </c>
       <c r="G91">
         <v>520722432</v>
